--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/搜打撤_刷怪波次配置表_SearchExtract_SearchExtractWaveSpawnConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/搜打撤_刷怪波次配置表_SearchExtract_SearchExtractWaveSpawnConfig.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Cursor\Gravedigger2026\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Mode2\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\CursorGame_Git\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Mode2\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="42">
   <si>
     <t>玩法配置ID</t>
   </si>
@@ -141,12 +141,21 @@
     <t>SearchExtract_01</t>
   </si>
   <si>
+    <t>SP_05</t>
+  </si>
+  <si>
+    <t>Monster_04</t>
+  </si>
+  <si>
+    <t>SP_06</t>
+  </si>
+  <si>
+    <t>SearchExtract_02</t>
+  </si>
+  <si>
     <t>SP_01</t>
   </si>
   <si>
-    <t>Monster_04</t>
-  </si>
-  <si>
     <t>SP_02</t>
   </si>
   <si>
@@ -154,9 +163,6 @@
   </si>
   <si>
     <t>SP_04</t>
-  </si>
-  <si>
-    <t>SearchExtract_02</t>
   </si>
   <si>
     <t>SP_11</t>
@@ -799,12 +805,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1154,17 +1157,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:I26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="18.625" customWidth="1"/>
-    <col min="2" max="2" width="14.375" customWidth="1"/>
+    <col min="1" max="1" width="18.6272727272727" customWidth="1"/>
+    <col min="2" max="2" width="14.3727272727273" customWidth="1"/>
     <col min="3" max="3" width="10.5" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="12.625" customWidth="1"/>
+    <col min="5" max="5" width="12.6272727272727" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="16.125" customWidth="1"/>
-    <col min="8" max="8" width="17.375" customWidth="1"/>
+    <col min="7" max="7" width="16.1272727272727" customWidth="1"/>
+    <col min="8" max="8" width="17.3727272727273" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1280,7 +1283,7 @@
         <v>29</v>
       </c>
       <c r="I4" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1294,7 +1297,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E5" s="2">
         <v>30</v>
@@ -1309,7 +1312,7 @@
         <v>29</v>
       </c>
       <c r="I5" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1323,7 +1326,7 @@
         <v>3</v>
       </c>
       <c r="D6" s="2">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E6" s="2">
         <v>30</v>
@@ -1332,13 +1335,13 @@
         <v>2</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>29</v>
       </c>
       <c r="I6" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1352,7 +1355,7 @@
         <v>4</v>
       </c>
       <c r="D7" s="2">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E7" s="2">
         <v>30</v>
@@ -1361,33 +1364,33 @@
         <v>2</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>29</v>
       </c>
       <c r="I7" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B8" s="2">
         <v>1</v>
       </c>
       <c r="C8" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D8" s="2">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E8" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F8" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>28</v>
@@ -1396,27 +1399,27 @@
         <v>29</v>
       </c>
       <c r="I8" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B9" s="2">
         <v>1</v>
       </c>
       <c r="C9" s="2">
+        <v>6</v>
+      </c>
+      <c r="D9" s="2">
+        <v>32</v>
+      </c>
+      <c r="E9" s="2">
+        <v>30</v>
+      </c>
+      <c r="F9" s="2">
         <v>2</v>
-      </c>
-      <c r="D9" s="2">
-        <v>10</v>
-      </c>
-      <c r="E9" s="2">
-        <v>25</v>
-      </c>
-      <c r="F9" s="2">
-        <v>3</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>30</v>
@@ -1425,50 +1428,50 @@
         <v>29</v>
       </c>
       <c r="I9" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B10" s="2">
         <v>1</v>
       </c>
       <c r="C10" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D10" s="2">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="E10" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F10" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>29</v>
       </c>
       <c r="I10" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B11" s="2">
         <v>1</v>
       </c>
       <c r="C11" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D11" s="2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E11" s="2">
         <v>25</v>
@@ -1483,21 +1486,21 @@
         <v>29</v>
       </c>
       <c r="I11" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="3">
+        <v>31</v>
+      </c>
+      <c r="B12" s="2">
+        <v>1</v>
+      </c>
+      <c r="C12" s="2">
         <v>2</v>
       </c>
-      <c r="C12" s="2">
-        <v>1</v>
-      </c>
       <c r="D12" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E12" s="2">
         <v>25</v>
@@ -1506,7 +1509,7 @@
         <v>3</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>29</v>
@@ -1517,16 +1520,16 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="3">
-        <v>2</v>
+        <v>31</v>
+      </c>
+      <c r="B13" s="2">
+        <v>1</v>
       </c>
       <c r="C13" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E13" s="2">
         <v>25</v>
@@ -1535,27 +1538,27 @@
         <v>3</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>29</v>
       </c>
       <c r="I13" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="3">
-        <v>2</v>
+        <v>31</v>
+      </c>
+      <c r="B14" s="2">
+        <v>1</v>
       </c>
       <c r="C14" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E14" s="2">
         <v>25</v>
@@ -1564,7 +1567,7 @@
         <v>3</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>29</v>
@@ -1575,16 +1578,16 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" s="3">
+        <v>31</v>
+      </c>
+      <c r="B15" s="2">
         <v>2</v>
       </c>
       <c r="C15" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D15" s="2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E15" s="2">
         <v>25</v>
@@ -1593,65 +1596,65 @@
         <v>3</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="I15" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B16" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E16" s="2">
         <v>25</v>
       </c>
       <c r="F16" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>29</v>
       </c>
       <c r="I16" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B17" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E17" s="2">
         <v>25</v>
       </c>
       <c r="F17" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>29</v>
@@ -1662,25 +1665,25 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B18" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E18" s="2">
         <v>25</v>
       </c>
       <c r="F18" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>29</v>
@@ -1691,16 +1694,16 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B19" s="2">
         <v>1</v>
       </c>
       <c r="C19" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D19" s="2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E19" s="2">
         <v>25</v>
@@ -1720,16 +1723,16 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B20" s="2">
         <v>1</v>
       </c>
       <c r="C20" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E20" s="2">
         <v>25</v>
@@ -1738,27 +1741,27 @@
         <v>4</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>29</v>
       </c>
       <c r="I20" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B21" s="2">
         <v>1</v>
       </c>
       <c r="C21" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E21" s="2">
         <v>25</v>
@@ -1767,27 +1770,27 @@
         <v>4</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>29</v>
       </c>
       <c r="I21" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B22" s="2">
         <v>1</v>
       </c>
       <c r="C22" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D22" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E22" s="2">
         <v>25</v>
@@ -1796,27 +1799,27 @@
         <v>4</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>29</v>
       </c>
       <c r="I22" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B23" s="2">
         <v>1</v>
       </c>
       <c r="C23" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D23" s="2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E23" s="2">
         <v>25</v>
@@ -1831,6 +1834,93 @@
         <v>29</v>
       </c>
       <c r="I23" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="2">
+        <v>1</v>
+      </c>
+      <c r="C24" s="2">
+        <v>2</v>
+      </c>
+      <c r="D24" s="2">
+        <v>10</v>
+      </c>
+      <c r="E24" s="2">
+        <v>25</v>
+      </c>
+      <c r="F24" s="2">
+        <v>4</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I24" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="2">
+        <v>1</v>
+      </c>
+      <c r="C25" s="2">
+        <v>3</v>
+      </c>
+      <c r="D25" s="2">
+        <v>15</v>
+      </c>
+      <c r="E25" s="2">
+        <v>25</v>
+      </c>
+      <c r="F25" s="2">
+        <v>4</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I25" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="2">
+        <v>1</v>
+      </c>
+      <c r="C26" s="2">
+        <v>4</v>
+      </c>
+      <c r="D26" s="2">
+        <v>20</v>
+      </c>
+      <c r="E26" s="2">
+        <v>25</v>
+      </c>
+      <c r="F26" s="2">
+        <v>4</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I26" s="2">
         <v>10</v>
       </c>
     </row>
